--- a/NRHS/Output/NRHS_Timetable_Final.xlsx
+++ b/NRHS/Output/NRHS_Timetable_Final.xlsx
@@ -701,7 +701,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (ENG)</t>
+          <t>UKG (A) (MATH)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (MATH)</t>
+          <t>UKG (A) (ENG)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -1026,7 +1026,11 @@
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr"/>
-      <c r="C16" s="7" t="inlineStr"/>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Class 10 (BIO)</t>
@@ -1072,11 +1076,7 @@
           <t>Class 10 (BIO)</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
-        </is>
-      </c>
+      <c r="C18" s="7" t="inlineStr"/>
       <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Class 9 (BIO)</t>
@@ -1099,12 +1099,12 @@
           <t>Class 8 (BIO)</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Class 9 (BIO)</t>
         </is>
       </c>
+      <c r="D19" s="7" t="inlineStr"/>
       <c r="E19" s="7" t="inlineStr"/>
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr"/>
@@ -1192,12 +1192,12 @@
       <c r="D23" s="7" t="inlineStr"/>
       <c r="E23" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr"/>
@@ -1265,12 +1265,12 @@
       <c r="C25" s="7" t="inlineStr"/>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
+          <t>Class 4 (MATH)</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1281,7 +1281,7 @@
       <c r="G25" s="7" t="inlineStr"/>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (MATH)</t>
+          <t>Class 6 (MATH)</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
@@ -1381,13 +1381,13 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (MATH)</t>
+          <t>Class 6 (MATH)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
+          <t>Class 4 (MATH)</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       <c r="G28" s="7" t="inlineStr"/>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (TEL)</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (MATH)</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (TEL)</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (HIN)</t>
+          <t>Class 1(A) (MATH)</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       <c r="E33" s="7" t="inlineStr"/>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (MATH)</t>
+          <t>Class 1(A) (G.K)</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (G.K)</t>
+          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -1610,27 +1610,27 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (EVS)</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (ENG)</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (TEL)</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (HIN)</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (MATH)</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (ENG)</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (TEL)</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (HIN)</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (EVS)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (ENG)</t>
+          <t>Class 1(A) (HIN)</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -1700,32 +1700,32 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (ENG)</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (ENG)</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (MATH)</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (TEL)</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (ENG)</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (MATH)</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (HIN)</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (EVS)</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (HIN)</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (PHY)</t>
+          <t>Class 7 (CHEM)</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (CHEM)</t>
+          <t>Class 6 (CHEM)</t>
         </is>
       </c>
       <c r="I59" s="8" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (G.K)</t>
+          <t>Class 7 (PHY)</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr"/>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (CHEM)</t>
+          <t>Class 7 (G.K)</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr"/>
@@ -2381,7 +2381,7 @@
       <c r="G61" s="7" t="inlineStr"/>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (PHY)</t>
+          <t>Class 7 (CHEM)</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr">
@@ -2399,7 +2399,7 @@
       <c r="B62" s="7" t="inlineStr"/>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (CHEM)</t>
+          <t>Class 6 (PHY)</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (PHY)</t>
+          <t>Class 7 (PHY)</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
@@ -2772,13 +2772,13 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (TEL)</t>
+          <t>Class 7 (TEL)</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr"/>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (TEL)</t>
+          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr"/>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (EVS)</t>
+          <t>UKG (B) (ENG)</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -2923,11 +2923,7 @@
           <t>UKG (B) (MATH)</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
+      <c r="G78" s="7" t="inlineStr"/>
       <c r="H78" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (MATH)</t>
@@ -3060,7 +3056,11 @@
           <t>UKG (B) (TEL)</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr"/>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (EVS)</t>
+        </is>
+      </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (EVS)</t>
@@ -3190,13 +3190,13 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr"/>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (ENG)</t>
+          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -3204,12 +3204,12 @@
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="G86" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="H86" s="7" t="inlineStr"/>
+      <c r="G86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
           <t>Class 3</t>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 5 (ENG)</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr"/>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (ENG)</t>
+          <t>Class 5 (ENG)</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr"/>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (ENG)</t>
+          <t>Class 6 (ENG)</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (TEL)</t>
+          <t>Class 4 (TEL)</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr"/>
@@ -3513,12 +3513,12 @@
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (TEL)</t>
+          <t>Class 5 (TEL)</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (TEL)</t>
+          <t>Class 3 (TEL)</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr"/>
@@ -3542,7 +3542,7 @@
       <c r="C96" s="7" t="inlineStr"/>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (TEL)</t>
+          <t>Class 4 (TEL)</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
@@ -3558,7 +3558,7 @@
       <c r="G96" s="7" t="inlineStr"/>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (TEL)</t>
+          <t>Class 5 (TEL)</t>
         </is>
       </c>
       <c r="I96" s="8" t="inlineStr">
@@ -3698,17 +3698,17 @@
       <c r="C100" s="7" t="inlineStr"/>
       <c r="D100" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="F100" s="7" t="inlineStr">
         <is>
           <t>Class 3 (TEL)</t>
-        </is>
-      </c>
-      <c r="F100" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr"/>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (SOC)</t>
+          <t>Class 6 (SOC)</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -3878,7 +3878,7 @@
       <c r="D106" s="7" t="inlineStr"/>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (SOC)</t>
+          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -3889,7 +3889,7 @@
       <c r="G106" s="7" t="inlineStr"/>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (SOC)</t>
+          <t>Class 4 (SOC)</t>
         </is>
       </c>
       <c r="I106" s="8" t="inlineStr">
@@ -3984,28 +3984,28 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (SOC)</t>
+          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (SOC)</t>
+          <t>Class 4 (SOC)</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr"/>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (SOC)</t>
+          <t>Class 3 (SOC)</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (SOC)</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr"/>
@@ -4341,12 +4341,12 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (EVS)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr"/>
@@ -4357,12 +4357,12 @@
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
+          <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
+          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="I123" s="7" t="inlineStr"/>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (BIO)</t>
+          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (EVS)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="I124" s="7" t="inlineStr"/>
@@ -4415,7 +4415,7 @@
       <c r="B125" s="7" t="inlineStr"/>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>Class 2 (G.K)</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (G.K)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (EVS)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr"/>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
+          <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
@@ -4500,17 +4500,17 @@
       <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
-      <c r="H127" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="I127" s="7" t="inlineStr"/>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (HIN)</t>
+          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (HIN)</t>
+          <t>Class 6 (HIN)</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
@@ -4744,11 +4744,7 @@
           <t>Class 7 (HIN)</t>
         </is>
       </c>
-      <c r="G135" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
+      <c r="G135" s="7" t="inlineStr"/>
       <c r="H135" s="7" t="inlineStr"/>
       <c r="I135" s="8" t="inlineStr">
         <is>
@@ -4764,27 +4760,31 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
-      <c r="C136" s="7" t="inlineStr">
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
         <is>
           <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="D136" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
       <c r="G136" s="7" t="inlineStr"/>
-      <c r="H136" s="7" t="inlineStr"/>
+      <c r="H136" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
       <c r="I136" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -4879,13 +4879,13 @@
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr"/>
-      <c r="C141" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (PHY)</t>
-        </is>
-      </c>
+      <c r="C141" s="7" t="inlineStr"/>
       <c r="D141" s="7" t="inlineStr"/>
-      <c r="E141" s="7" t="inlineStr"/>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
       <c r="F141" s="7" t="inlineStr"/>
       <c r="G141" s="7" t="inlineStr"/>
       <c r="H141" s="7" t="inlineStr"/>
@@ -4936,13 +4936,13 @@
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr"/>
-      <c r="C144" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
+      <c r="C144" s="7" t="inlineStr"/>
       <c r="D144" s="7" t="inlineStr"/>
-      <c r="E144" s="7" t="inlineStr"/>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (PHY)</t>
+        </is>
+      </c>
       <c r="F144" s="7" t="inlineStr"/>
       <c r="G144" s="7" t="inlineStr"/>
       <c r="H144" s="7" t="inlineStr"/>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>LKG (ENG)</t>
+          <t>LKG (EVS)</t>
         </is>
       </c>
       <c r="C149" s="7" t="inlineStr">
@@ -5106,7 +5106,7 @@
       <c r="G150" s="7" t="inlineStr"/>
       <c r="H150" s="7" t="inlineStr">
         <is>
-          <t>LKG (ENG)</t>
+          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="I150" s="8" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="E151" s="7" t="inlineStr">
         <is>
-          <t>LKG (MATH)</t>
+          <t>LKG (ENG)</t>
         </is>
       </c>
       <c r="F151" s="7" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="B152" s="7" t="inlineStr">
         <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
           <t>LKG (EVS)</t>
-        </is>
-      </c>
-      <c r="C152" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="B153" s="7" t="inlineStr">
         <is>
-          <t>LKG (MATH)</t>
+          <t>LKG (EVS)</t>
         </is>
       </c>
       <c r="C153" s="7" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>LKG (EVS)</t>
+          <t>LKG (ENG)</t>
         </is>
       </c>
       <c r="C154" s="7" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>LKG (EVS)</t>
+          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
@@ -5593,22 +5593,22 @@
       </c>
       <c r="B167" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (MATH)</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (MATH)</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (TEL)</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (HIN)</t>
-        </is>
-      </c>
-      <c r="C167" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (MATH)</t>
-        </is>
-      </c>
-      <c r="D167" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (TEL)</t>
-        </is>
-      </c>
-      <c r="E167" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (MATH)</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
@@ -5941,7 +5941,7 @@
       <c r="B177" s="7" t="inlineStr"/>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (COMP)</t>
+          <t>Class 4 (COMP)</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
@@ -5982,7 +5982,11 @@
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
-      <c r="G178" s="7" t="inlineStr"/>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (COMP)</t>
+        </is>
+      </c>
       <c r="H178" s="7" t="inlineStr"/>
       <c r="I178" s="7" t="inlineStr"/>
     </row>
@@ -6058,7 +6062,7 @@
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (COMP)</t>
+          <t>Class 6 (COMP)</t>
         </is>
       </c>
       <c r="E181" s="7" t="inlineStr">
@@ -6067,11 +6071,7 @@
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
-      <c r="G181" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (COMP)</t>
-        </is>
-      </c>
+      <c r="G181" s="7" t="inlineStr"/>
       <c r="H181" s="7" t="inlineStr"/>
       <c r="I181" s="7" t="inlineStr"/>
     </row>
@@ -6150,12 +6150,12 @@
       <c r="F185" s="7" t="inlineStr"/>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (P.E.T)</t>
+          <t>Class 5 (P.E.T)</t>
         </is>
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (P.E.T)</t>
+          <t>Class 7 (P.E.T)</t>
         </is>
       </c>
       <c r="I185" s="7" t="inlineStr"/>
@@ -6196,7 +6196,7 @@
       <c r="F187" s="7" t="inlineStr"/>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (P.E.T)</t>
+          <t>Class 4 (P.E.T)</t>
         </is>
       </c>
       <c r="H187" s="7" t="inlineStr">
@@ -6238,7 +6238,7 @@
       <c r="F189" s="7" t="inlineStr"/>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (P.E.T)</t>
+          <t>Class 6 (P.E.T)</t>
         </is>
       </c>
       <c r="H189" s="7" t="inlineStr">
@@ -6261,12 +6261,12 @@
       <c r="F190" s="7" t="inlineStr"/>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (P.E.T)</t>
+          <t>Class 5 (P.E.T)</t>
         </is>
       </c>
       <c r="H190" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (P.E.T)</t>
+          <t>Class 1(A) (P.E.T)</t>
         </is>
       </c>
       <c r="I190" s="7" t="inlineStr"/>
@@ -6578,7 +6578,7 @@
       <c r="C2" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -6590,19 +6590,19 @@
       <c r="E2" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (MATH)</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(HIN)</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
@@ -6686,7 +6686,7 @@
       <c r="F3" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(TEL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -6703,14 +6703,14 @@
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
           <t>P.SATYAVENI
 (TEL)</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -6870,7 +6870,7 @@
       <c r="G5" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(MATH)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -6887,14 +6887,14 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
           <t>CHANDINI
 (MATH)</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -6974,14 +6974,14 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
           <t>P.SATYAVENI
 (TEL)</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -7058,8 +7058,8 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>N.NAVYA
-(ENG)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -7070,8 +7070,8 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+          <t>P.E.T Instructor
+(P.E.T)</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -7083,7 +7083,7 @@
       <c r="M7" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(PHY)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -7154,26 +7154,26 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
@@ -7395,7 +7395,7 @@
       <c r="D11" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -7407,7 +7407,7 @@
       <c r="F11" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(HIN)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -7430,8 +7430,8 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(EVS)</t>
+          <t>VINAY
+(COMP)</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -7442,14 +7442,14 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>S.GAYATHRI
+(BIO)</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(G.K)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -7458,10 +7458,9 @@
 (MATH)</t>
         </is>
       </c>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>SAIRAM
-(PHY)</t>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
@@ -7515,19 +7514,19 @@
       <c r="I12" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -7643,9 +7642,10 @@
 (TEL)</t>
         </is>
       </c>
-      <c r="P13" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
       <c r="F14" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(MATH)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -7758,8 +7758,8 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>MAHA LAKSHMI
-(ENG)</t>
+          <t>P.E.T Instructor
+(P.E.T)</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -7783,7 +7783,7 @@
       <c r="I15" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
@@ -7807,7 +7807,7 @@
       <c r="M15" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(CHEM)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
@@ -7837,7 +7837,7 @@
       <c r="C16" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -7872,20 +7872,20 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
           <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
+(EVS)</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
 (TEL)</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -8064,20 +8064,20 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr">
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
@@ -8175,9 +8175,10 @@
 (SOC)</t>
         </is>
       </c>
-      <c r="N19" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
       <c r="O19" s="7" t="inlineStr">
@@ -8248,14 +8249,14 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
           <t>SAI KEERTHI
 (HIN)</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -8291,7 +8292,7 @@
       <c r="C21" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -8332,14 +8333,14 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
           <t>R.KAMALA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -8486,8 +8487,8 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>CHANDRAKALA
-(G.K)</t>
+          <t>VINAY
+(COMP)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -8498,20 +8499,20 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
+          <t>CHANDRAKALA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
@@ -8595,31 +8596,31 @@
       <c r="I24" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(PHY)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
@@ -8745,7 +8746,7 @@
       <c r="C26" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -8763,7 +8764,7 @@
       <c r="F26" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -8835,7 +8836,7 @@
       <c r="C27" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -8865,7 +8866,7 @@
       <c r="H27" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(EVS)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -8889,7 +8890,7 @@
       <c r="L27" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(CHEM)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -9120,7 +9121,7 @@
       <c r="F30" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -9468,7 +9469,7 @@
       <c r="C34" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -9588,7 +9589,7 @@
       <c r="H35" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(G.K)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
@@ -9621,10 +9622,9 @@
 (MATH)</t>
         </is>
       </c>
-      <c r="N35" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
+      <c r="N35" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
       <c r="O35" s="7" t="inlineStr">
@@ -9633,10 +9633,9 @@
 (ENG)</t>
         </is>
       </c>
-      <c r="P35" s="7" t="inlineStr">
-        <is>
-          <t>SAIRAM
-(PHY)</t>
+      <c r="P35" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9683,7 @@
       <c r="I36" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
@@ -9807,9 +9806,10 @@
 (MATH)</t>
         </is>
       </c>
-      <c r="O37" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
         </is>
       </c>
       <c r="P37" s="12" t="inlineStr">
@@ -9927,50 +9927,50 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
+          <t>MAHA LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -10192,7 +10192,7 @@
       <c r="C42" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -10210,7 +10210,7 @@
       <c r="F42" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(TEL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -10233,20 +10233,20 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="inlineStr">
-        <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="L42" s="7" t="inlineStr">
+      <c r="K42" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(BIO)</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -10323,22 +10323,22 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="K43" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="L43" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
@@ -10351,9 +10351,10 @@
 (COMP)</t>
         </is>
       </c>
-      <c r="O43" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
@@ -10371,7 +10372,7 @@
       <c r="C44" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -10412,22 +10413,22 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="K44" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L44" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
@@ -10440,10 +10441,9 @@
 (TEL)</t>
         </is>
       </c>
-      <c r="O44" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
+      <c r="O44" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
       <c r="P44" s="7" t="inlineStr">
@@ -10479,7 +10479,7 @@
       <c r="F45" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(EVS)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
       <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (PHY)</t>
-        </is>
-      </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
         </is>
       </c>
       <c r="N45" s="12" t="inlineStr">
@@ -10556,7 +10556,7 @@
       <c r="D46" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -10585,16 +10585,16 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
           <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
@@ -10603,14 +10603,14 @@
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="M46" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
@@ -10657,8 +10657,8 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>CHANDRAKALA
+(EVS)</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -10669,38 +10669,38 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>CHANDRAKALA
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
 (MATH)</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="J47" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L47" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
@@ -10766,7 +10766,7 @@
       <c r="I48" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
@@ -10777,20 +10777,20 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="L48" s="7" t="inlineStr">
-        <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="M48" s="7" t="inlineStr">
+      <c r="L48" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
+        </is>
+      </c>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">

--- a/NRHS/Output/NRHS_Timetable_Final.xlsx
+++ b/NRHS/Output/NRHS_Timetable_Final.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,11 +41,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -186,7 +181,7 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -653,7 +648,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (HIN)</t>
+          <t>UKG (A) (ORAL)</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -663,23 +658,23 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (TEL)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (MATH)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (EVS)</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (TEL)</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ORAL)</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr"/>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (ENG)</t>
+          <t>UKG (A) (MATH)</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
@@ -696,37 +691,37 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (TEL)</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (MATH)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (HIN)</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (ENG)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (MATH)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (MATH)</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (ORAL)</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (EVS)</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (EVS)</t>
-        </is>
-      </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (TEL)</t>
+          <t>UKG (A) (ENG)</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -743,19 +738,19 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (TEL)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (EVS)</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (ORAL)</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ENG)</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (TEL)</t>
-        </is>
-      </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (MATH)</t>
@@ -763,17 +758,13 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (ENG)</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
           <t>UKG (A) (HIN)</t>
         </is>
       </c>
+      <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (EVS)</t>
+          <t>UKG (A) (MATH)</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -790,33 +781,33 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (TEL)</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (MATH)</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (ENG)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (EVS)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (MATH)</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (TEL)</t>
-        </is>
-      </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (ENG)</t>
+          <t>UKG (A) (ORAL)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr"/>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (ORAL)</t>
+          <t>UKG (A) (HIN)</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
@@ -833,33 +824,37 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (EVS)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (TEL)</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (EVS)</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (EVS)</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (ORAL)</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (ENG)</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (EVS)</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ENG)</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (HIN)</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ORAL)</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -876,24 +871,24 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (ENG)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (ORAL)</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (TEL)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (ENG)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (MATH)</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (TEL)</t>
-        </is>
-      </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (ENG)</t>
@@ -906,14 +901,10 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (MATH)</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>UKG (A)</t>
-        </is>
-      </c>
+          <t>UKG (A) (ENG)</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -984,7 +975,11 @@
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr"/>
-      <c r="C14" s="7" t="inlineStr"/>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Class 10 (BIO)</t>
@@ -1005,12 +1000,12 @@
       <c r="B15" s="7" t="inlineStr"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (BIO)</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
@@ -1028,12 +1023,12 @@
       <c r="B16" s="7" t="inlineStr"/>
       <c r="C16" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (BIO)</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (BIO)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -1048,15 +1043,15 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr"/>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>Class 9 (BIO)</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr"/>
@@ -1071,15 +1066,15 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Class 10 (BIO)</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -1094,17 +1089,17 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Class 8 (BIO)</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr"/>
       <c r="E19" s="7" t="inlineStr"/>
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr"/>
@@ -1184,26 +1179,26 @@
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr"/>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr"/>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
+          <t>Class 4 (MATH)</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
@@ -1220,31 +1215,35 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr"/>
       <c r="E24" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr"/>
       <c r="I24" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -1262,20 +1261,20 @@
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr"/>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr"/>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr"/>
@@ -1303,23 +1302,23 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr"/>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr"/>
@@ -1335,31 +1334,31 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr"/>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
+      <c r="C27" s="7" t="inlineStr"/>
       <c r="D27" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
@@ -1381,13 +1380,13 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
+          <t>Class 4 (MATH)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (MATH)</t>
+          <t>Class 6 (MATH)</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -1395,17 +1394,13 @@
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>Class 7</t>
-        </is>
-      </c>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1477,23 +1472,23 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (ENG)</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (MATH)</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (TEL)</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (MATH)</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (HIN)</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr"/>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (G.K)</t>
+          <t>Class 1(A) (HIN)</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -1525,15 +1520,19 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (TEL)</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (MATH)</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (ENG)</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr"/>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (HIN)</t>
+        </is>
+      </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (G.K)</t>
@@ -1541,7 +1540,7 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (TEL)</t>
+          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -1563,7 +1562,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (HIN)</t>
+          <t>Class 1(A) (ENG)</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -1573,22 +1572,18 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (TEL)</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (ENG)</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (EVS)</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (TEL)</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (ENG)</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -1610,27 +1605,27 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (MATH)</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (HIN)</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (TEL)</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (G.K)</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (EVS)</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (ENG)</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (TEL)</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (HIN)</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (MATH)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -1658,27 +1653,27 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (HIN)</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (MATH)</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (EVS)</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (MATH)</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (ENG)</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (TEL)</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (ENG)</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (HIN)</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -1705,39 +1700,35 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (MATH)</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (ENG)</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (MATH)</t>
-        </is>
-      </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (HIN)</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (EVS)</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (TEL)</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (HIN)</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (EVS)</t>
-        </is>
-      </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>Class 1(A)</t>
-        </is>
-      </c>
+      <c r="I37" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -1814,10 +1805,14 @@
       <c r="F41" s="7" t="inlineStr"/>
       <c r="G41" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="8" t="inlineStr">
         <is>
           <t>Class 9 (MATH)</t>
@@ -1842,7 +1837,7 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (MATH)</t>
+          <t>Class 10 (MATH)</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
@@ -1889,12 +1884,12 @@
       <c r="D44" s="7" t="inlineStr"/>
       <c r="E44" s="7" t="inlineStr"/>
       <c r="F44" s="7" t="inlineStr"/>
-      <c r="G44" s="7" t="inlineStr"/>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>Class 9 (MATH)</t>
         </is>
       </c>
+      <c r="H44" s="7" t="inlineStr"/>
       <c r="I44" s="8" t="inlineStr">
         <is>
           <t>Class 9 (MATH)</t>
@@ -1919,12 +1914,12 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
           <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
         </is>
       </c>
     </row>
@@ -1941,19 +1936,15 @@
       <c r="F46" s="7" t="inlineStr"/>
       <c r="G46" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
+      <c r="I46" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -2025,31 +2016,31 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (G.K)</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr"/>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr"/>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (G.K)</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr"/>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
+      <c r="H50" s="7" t="inlineStr"/>
       <c r="I50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2063,23 +2054,27 @@
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr"/>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
+      <c r="D51" s="7" t="inlineStr"/>
       <c r="E51" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr"/>
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr"/>
     </row>
@@ -2089,28 +2084,28 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr"/>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr"/>
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr"/>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
+      <c r="G52" s="7" t="inlineStr"/>
       <c r="H52" s="7" t="inlineStr"/>
       <c r="I52" s="7" t="inlineStr"/>
     </row>
@@ -2125,20 +2120,20 @@
           <t>Class 10 (ENG)</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
+      <c r="C53" s="7" t="inlineStr"/>
       <c r="D53" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (ENG)</t>
+          <t>Class 10 (ENG)</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr"/>
@@ -2151,29 +2146,33 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr"/>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr"/>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr"/>
-      <c r="G54" s="7" t="inlineStr"/>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
+      <c r="H54" s="7" t="inlineStr"/>
       <c r="I54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2182,29 +2181,29 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr"/>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr"/>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr"/>
       <c r="G55" s="7" t="inlineStr"/>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
+      <c r="H55" s="7" t="inlineStr"/>
       <c r="I55" s="7" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2277,33 +2276,33 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (G.K)</t>
+          <t>Class 8 (PHY)</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (CHEM)</t>
+          <t>Class 9 (CHEM)</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (CHEM)</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr"/>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (PHY)</t>
-        </is>
-      </c>
+      <c r="F59" s="7" t="inlineStr"/>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (CHEM)</t>
+          <t>Class 6 (CHEM)</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (CHEM)</t>
+          <t>Class 6 (PHY)</t>
         </is>
       </c>
       <c r="I59" s="8" t="inlineStr">
@@ -2320,31 +2319,35 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (PHY)</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>Class 7 (PHY)</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr"/>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (CHEM)</t>
+          <t>Class 10 (CHEM)</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (G.K)</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr"/>
+          <t>Class 5 (G.K)</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (CHEM)</t>
+        </is>
+      </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
           <t>Class 5</t>
@@ -2362,26 +2365,34 @@
           <t>Class 8 (CHEM)</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr"/>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (CHEM)</t>
+        </is>
+      </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (CHEM)</t>
+          <t>Class 6 (CHEM)</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (G.K)</t>
+          <t>Class 10 (CHEM)</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (PHY)</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="G61" s="7" t="inlineStr"/>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (CHEM)</t>
+          <t>Class 8 (PHY)</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr">
@@ -2396,26 +2407,30 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr"/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (CHEM)</t>
+        </is>
+      </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (PHY)</t>
+          <t>Class 9 (CHEM)</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (PHY)</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr"/>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>Class 4 (G.K)</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr"/>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (CHEM)</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -2437,33 +2452,33 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (CHEM)</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (CHEM)</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (G.K)</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (CHEM)</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (G.K)</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (CHEM)</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr"/>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (CHEM)</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (CHEM)</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
@@ -2480,36 +2495,36 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (PHY)</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (CHEM)</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (CHEM)</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr"/>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (CHEM)</t>
-        </is>
-      </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (PHY)</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="G64" s="7" t="inlineStr"/>
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (G.K)</t>
+        </is>
+      </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (CHEM)</t>
-        </is>
-      </c>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>Class 5</t>
-        </is>
-      </c>
+          <t>Class 8 (CHEM)</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -2579,31 +2594,31 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr"/>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr"/>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (TEL)</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr"/>
+      <c r="H68" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr"/>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (TEL)</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr"/>
@@ -2622,12 +2637,12 @@
       <c r="C69" s="7" t="inlineStr"/>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
+          <t>Class 9 (TEL)</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (TEL)</t>
+          <t>Class 7 (TEL)</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -2638,7 +2653,7 @@
       <c r="G69" s="7" t="inlineStr"/>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (TEL)</t>
+          <t>Class 8 (TEL)</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr"/>
@@ -2659,15 +2674,15 @@
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr"/>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr"/>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
@@ -2686,7 +2701,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
+          <t>Class 9 (TEL)</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -2697,7 +2712,7 @@
       <c r="D71" s="7" t="inlineStr"/>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (TEL)</t>
+          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -2707,7 +2722,7 @@
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (TEL)</t>
+          <t>Class 8 (TEL)</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr"/>
@@ -2721,31 +2736,31 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr"/>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr"/>
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr"/>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
+      <c r="H72" s="7" t="inlineStr"/>
       <c r="I72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
@@ -2759,12 +2774,12 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr"/>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
+      <c r="D73" s="7" t="inlineStr"/>
       <c r="E73" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
@@ -2772,13 +2787,13 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (TEL)</t>
+          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr"/>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (TEL)</t>
+          <t>Class 7 (TEL)</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr"/>
@@ -2853,37 +2868,37 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (ENG)</t>
+          <t>UKG (B) (MATH)</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (ENG)</t>
+          <t>UKG (B) (MATH)</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (EVS)</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (HIN)</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (TEL)</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (HIN)</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (EVS)</t>
         </is>
       </c>
-      <c r="G77" s="7" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (ORAL)</t>
-        </is>
-      </c>
-      <c r="H77" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (EVS)</t>
         </is>
       </c>
       <c r="I77" s="8" t="inlineStr">
@@ -2900,33 +2915,33 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (TEL)</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (HIN)</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (MATH)</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (TEL)</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="F78" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (ORAL)</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (MATH)</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr"/>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (MATH)</t>
+          <t>UKG (B) (EVS)</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
@@ -2943,37 +2958,33 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (EVS)</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (EVS)</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (TEL)</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (ORAL)</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (HIN)</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (MATH)</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ORAL)</t>
-        </is>
-      </c>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (HIN)</t>
-        </is>
-      </c>
-      <c r="H79" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (TEL)</t>
         </is>
       </c>
       <c r="I79" s="8" t="inlineStr">
@@ -2995,28 +3006,32 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (HIN)</t>
+          <t>UKG (B) (EVS)</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (MATH)</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (TEL)</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (ORAL)</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (MATH)</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (TEL)</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr"/>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (EVS)</t>
+          <t>UKG (B) (ENG)</t>
         </is>
       </c>
       <c r="I80" s="8" t="inlineStr">
@@ -3033,37 +3048,33 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (MATH)</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (HIN)</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (EVS)</t>
-        </is>
-      </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (TEL)</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (MATH)</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr"/>
+      <c r="H81" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (ORAL)</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (MATH)</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (TEL)</t>
-        </is>
-      </c>
-      <c r="G81" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (EVS)</t>
-        </is>
-      </c>
-      <c r="H81" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (EVS)</t>
         </is>
       </c>
       <c r="I81" s="8" t="inlineStr">
@@ -3080,40 +3091,40 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (TEL)</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (HIN)</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (ORAL)</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (EVS)</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (MATH)</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ORAL)</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (TEL)</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (HIN)</t>
-        </is>
-      </c>
-      <c r="G82" s="7" t="inlineStr"/>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (EVS)</t>
-        </is>
-      </c>
-      <c r="I82" s="8" t="inlineStr">
-        <is>
-          <t>UKG (B)</t>
-        </is>
-      </c>
+      <c r="I82" s="7" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -3190,24 +3201,28 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="inlineStr"/>
+          <t>Class 5 (ENG)</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr"/>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 5 (ENG)</t>
         </is>
       </c>
       <c r="I86" s="8" t="inlineStr">
@@ -3229,28 +3244,28 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (ENG)</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (ENG)</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr"/>
       <c r="F87" s="7" t="inlineStr">
         <is>
           <t>Class 4 (ENG)</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (ENG)</t>
-        </is>
-      </c>
+      <c r="G87" s="7" t="inlineStr"/>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (ENG)</t>
+          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="I87" s="8" t="inlineStr">
@@ -3272,7 +3287,7 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (ENG)</t>
+          <t>Class 6 (ENG)</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -3283,12 +3298,12 @@
       <c r="E88" s="7" t="inlineStr"/>
       <c r="F88" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
@@ -3315,25 +3330,21 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (ENG)</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
           <t>Class 2 (ENG)</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr"/>
+      <c r="D89" s="7" t="inlineStr"/>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr"/>
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="8" t="inlineStr">
         <is>
@@ -3349,7 +3360,7 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (ENG)</t>
+          <t>Class 5 (ENG)</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
@@ -3405,12 +3416,12 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr"/>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr"/>
       <c r="G91" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
@@ -3418,14 +3429,10 @@
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="I91" s="8" t="inlineStr">
-        <is>
-          <t>Class 3</t>
-        </is>
-      </c>
+          <t>Class 5 (ENG)</t>
+        </is>
+      </c>
+      <c r="I91" s="7" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -3497,30 +3504,26 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr"/>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (TEL)</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="D95" s="7" t="inlineStr"/>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t>LKG (TEL)</t>
-        </is>
-      </c>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (TEL)</t>
-        </is>
-      </c>
+      <c r="G95" s="7" t="inlineStr"/>
       <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="8" t="inlineStr">
         <is>
@@ -3539,28 +3542,28 @@
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr"/>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>LKG (TEL)</t>
+        </is>
+      </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>LKG (TEL)</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr"/>
+      <c r="G96" s="7" t="inlineStr">
         <is>
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="G96" s="7" t="inlineStr"/>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
+      <c r="H96" s="7" t="inlineStr"/>
       <c r="I96" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3580,25 +3583,25 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (TEL)</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>LKG (TEL)</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr"/>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (TEL)</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>LKG (TEL)</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
+      <c r="G97" s="7" t="inlineStr"/>
       <c r="H97" s="7" t="inlineStr"/>
       <c r="I97" s="8" t="inlineStr">
         <is>
@@ -3614,15 +3617,19 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (TEL)</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (TEL)</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr"/>
       <c r="E98" s="7" t="inlineStr">
         <is>
           <t>LKG (TEL)</t>
@@ -3630,14 +3637,10 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr">
-        <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
+      <c r="G98" s="7" t="inlineStr"/>
       <c r="H98" s="7" t="inlineStr"/>
       <c r="I98" s="8" t="inlineStr">
         <is>
@@ -3656,28 +3659,28 @@
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr"/>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>LKG (TEL)</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr"/>
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>LKG (TEL)</t>
-        </is>
-      </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="G99" s="7" t="inlineStr"/>
-      <c r="H99" s="7" t="inlineStr">
+      <c r="G99" s="7" t="inlineStr">
         <is>
           <t>Class 3 (TEL)</t>
         </is>
       </c>
+      <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3695,29 +3698,29 @@
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr"/>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
+          <t>LKG (TEL)</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr"/>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="F100" s="7" t="inlineStr">
+      <c r="G100" s="7" t="inlineStr"/>
+      <c r="H100" s="7" t="inlineStr">
         <is>
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr"/>
-      <c r="H100" s="7" t="inlineStr"/>
-      <c r="I100" s="8" t="inlineStr">
-        <is>
-          <t>Class 2</t>
-        </is>
-      </c>
+      <c r="I100" s="7" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -3787,33 +3790,33 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B104" s="7" t="inlineStr"/>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr"/>
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="E104" s="7" t="inlineStr">
+      <c r="F104" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="F104" s="7" t="inlineStr"/>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="H104" s="7" t="inlineStr">
-        <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
+      <c r="H104" s="7" t="inlineStr"/>
       <c r="I104" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -3833,20 +3836,20 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (SOC)</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr"/>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (SOC)</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
+      <c r="F105" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="F105" s="7" t="inlineStr"/>
       <c r="G105" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
@@ -3870,12 +3873,12 @@
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="C106" s="7" t="inlineStr">
+      <c r="C106" s="7" t="inlineStr"/>
+      <c r="D106" s="7" t="inlineStr">
         <is>
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="D106" s="7" t="inlineStr"/>
       <c r="E106" s="7" t="inlineStr">
         <is>
           <t>Class 5 (SOC)</t>
@@ -3914,17 +3917,17 @@
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="D107" s="7" t="inlineStr"/>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
+      <c r="F107" s="7" t="inlineStr"/>
       <c r="G107" s="7" t="inlineStr">
         <is>
           <t>Class 7 (SOC)</t>
@@ -3948,12 +3951,12 @@
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="C108" s="7" t="inlineStr">
+      <c r="C108" s="7" t="inlineStr"/>
+      <c r="D108" s="7" t="inlineStr">
         <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="D108" s="7" t="inlineStr"/>
       <c r="E108" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
@@ -3964,12 +3967,12 @@
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="G108" s="7" t="inlineStr">
+      <c r="G108" s="7" t="inlineStr"/>
+      <c r="H108" s="7" t="inlineStr">
         <is>
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="H108" s="7" t="inlineStr"/>
       <c r="I108" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -3984,36 +3987,32 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr"/>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (SOC)</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr">
+      <c r="G109" s="7" t="inlineStr"/>
+      <c r="H109" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="D109" s="7" t="inlineStr"/>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (SOC)</t>
-        </is>
-      </c>
-      <c r="H109" s="7" t="inlineStr"/>
-      <c r="I109" s="8" t="inlineStr">
-        <is>
-          <t>Class 6</t>
-        </is>
-      </c>
+      <c r="I109" s="7" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -4093,7 +4092,11 @@
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr"/>
-      <c r="H113" s="7" t="inlineStr"/>
+      <c r="H113" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
       <c r="I113" s="8" t="inlineStr">
         <is>
           <t>Class 8 (HIN)</t>
@@ -4115,11 +4118,7 @@
           <t>Class 10 (HIN)</t>
         </is>
       </c>
-      <c r="G114" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (HIN)</t>
-        </is>
-      </c>
+      <c r="G114" s="7" t="inlineStr"/>
       <c r="H114" s="7" t="inlineStr"/>
       <c r="I114" s="8" t="inlineStr">
         <is>
@@ -4142,12 +4141,12 @@
           <t>Class 10 (HIN)</t>
         </is>
       </c>
-      <c r="G115" s="7" t="inlineStr"/>
-      <c r="H115" s="7" t="inlineStr">
+      <c r="G115" s="7" t="inlineStr">
         <is>
           <t>Class 8 (HIN)</t>
         </is>
       </c>
+      <c r="H115" s="7" t="inlineStr"/>
       <c r="I115" s="8" t="inlineStr">
         <is>
           <t>Class 9 (HIN)</t>
@@ -4169,11 +4168,15 @@
           <t>Class 9 (HIN)</t>
         </is>
       </c>
-      <c r="G116" s="7" t="inlineStr"/>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
       <c r="H116" s="7" t="inlineStr"/>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>Class 10 (HIN)</t>
+          <t>Class 8 (HIN)</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4196,11 @@
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr"/>
-      <c r="H117" s="7" t="inlineStr"/>
+      <c r="H117" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
           <t>Class 8 (HIN)</t>
@@ -4215,17 +4222,9 @@
           <t>Class 9 (HIN)</t>
         </is>
       </c>
-      <c r="G118" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (HIN)</t>
-        </is>
-      </c>
+      <c r="G118" s="7" t="inlineStr"/>
       <c r="H118" s="7" t="inlineStr"/>
-      <c r="I118" s="8" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
+      <c r="I118" s="7" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -4297,7 +4296,7 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (BIO)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
@@ -4307,15 +4306,15 @@
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr"/>
-      <c r="F122" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr"/>
       <c r="G122" s="7" t="inlineStr">
         <is>
           <t>Class 4 (EVS)</t>
@@ -4323,7 +4322,7 @@
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (EVS)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="I122" s="7" t="inlineStr"/>
@@ -4334,35 +4333,31 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B123" s="7" t="inlineStr">
+      <c r="B123" s="7" t="inlineStr"/>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (G.K)</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr"/>
+      <c r="H123" s="7" t="inlineStr">
         <is>
           <t>Class 7 (BIO)</t>
-        </is>
-      </c>
-      <c r="C123" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
-      <c r="D123" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr"/>
-      <c r="F123" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (G.K)</t>
-        </is>
-      </c>
-      <c r="G123" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="H123" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="I123" s="7" t="inlineStr"/>
@@ -4388,12 +4383,12 @@
           <t>Class 2 (EVS)</t>
         </is>
       </c>
-      <c r="E124" s="7" t="inlineStr"/>
-      <c r="F124" s="7" t="inlineStr">
+      <c r="E124" s="7" t="inlineStr">
         <is>
           <t>Class 7 (BIO)</t>
         </is>
       </c>
+      <c r="F124" s="7" t="inlineStr"/>
       <c r="G124" s="7" t="inlineStr">
         <is>
           <t>Class 3 (EVS)</t>
@@ -4412,26 +4407,30 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B125" s="7" t="inlineStr"/>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr"/>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (G.K)</t>
         </is>
       </c>
-      <c r="D125" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="inlineStr">
+      <c r="G125" s="7" t="inlineStr">
         <is>
           <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="F125" s="7" t="inlineStr"/>
-      <c r="G125" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr"/>
@@ -4445,33 +4444,33 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (BIO)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (EVS)</t>
         </is>
       </c>
-      <c r="D126" s="7" t="inlineStr">
+      <c r="F126" s="7" t="inlineStr"/>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr"/>
-      <c r="F126" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="G126" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="H126" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="I126" s="7" t="inlineStr"/>
@@ -4484,7 +4483,7 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (BIO)</t>
+          <t>Class 4 (EVS)</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
@@ -4494,23 +4493,23 @@
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
+          <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (EVS)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="I127" s="7" t="inlineStr"/>
@@ -4590,12 +4589,12 @@
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="D131" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr"/>
@@ -4623,24 +4622,28 @@
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="C132" s="7" t="inlineStr">
+      <c r="C132" s="7" t="inlineStr"/>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
         <is>
           <t>Class 3 (HIN)</t>
         </is>
       </c>
-      <c r="D132" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr"/>
+      <c r="H132" s="7" t="inlineStr">
         <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
-      <c r="F132" s="7" t="inlineStr"/>
-      <c r="G132" s="7" t="inlineStr"/>
-      <c r="H132" s="7" t="inlineStr"/>
       <c r="I132" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -4653,28 +4656,28 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B133" s="7" t="inlineStr">
+      <c r="B133" s="7" t="inlineStr"/>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
         <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
-      <c r="C133" s="7" t="inlineStr">
+      <c r="E133" s="7" t="inlineStr">
         <is>
           <t>Class 3 (HIN)</t>
         </is>
       </c>
-      <c r="D133" s="7" t="inlineStr">
+      <c r="F133" s="7" t="inlineStr"/>
+      <c r="G133" s="7" t="inlineStr">
         <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="E133" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
-      <c r="F133" s="7" t="inlineStr"/>
-      <c r="G133" s="7" t="inlineStr"/>
       <c r="H133" s="7" t="inlineStr"/>
       <c r="I133" s="8" t="inlineStr">
         <is>
@@ -4696,12 +4699,12 @@
       <c r="C134" s="7" t="inlineStr"/>
       <c r="D134" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
@@ -4730,18 +4733,18 @@
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr"/>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="D135" s="7" t="inlineStr"/>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="F135" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr"/>
@@ -4760,36 +4763,28 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (HIN)</t>
-        </is>
-      </c>
-      <c r="C136" s="7" t="inlineStr">
-        <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
+      <c r="C136" s="7" t="inlineStr"/>
       <c r="D136" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (HIN)</t>
         </is>
       </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="F136" s="7" t="inlineStr"/>
       <c r="G136" s="7" t="inlineStr"/>
-      <c r="H136" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
-      <c r="I136" s="8" t="inlineStr">
-        <is>
-          <t>Class 4</t>
-        </is>
-      </c>
+      <c r="H136" s="7" t="inlineStr"/>
+      <c r="I136" s="7" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -4859,14 +4854,18 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B140" s="7" t="inlineStr">
+      <c r="B140" s="7" t="inlineStr"/>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr"/>
+      <c r="E140" s="7" t="inlineStr">
         <is>
           <t>Class 9 (PHY)</t>
         </is>
       </c>
-      <c r="C140" s="7" t="inlineStr"/>
-      <c r="D140" s="7" t="inlineStr"/>
-      <c r="E140" s="7" t="inlineStr"/>
       <c r="F140" s="7" t="inlineStr"/>
       <c r="G140" s="7" t="inlineStr"/>
       <c r="H140" s="7" t="inlineStr"/>
@@ -4881,11 +4880,7 @@
       <c r="B141" s="7" t="inlineStr"/>
       <c r="C141" s="7" t="inlineStr"/>
       <c r="D141" s="7" t="inlineStr"/>
-      <c r="E141" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
+      <c r="E141" s="7" t="inlineStr"/>
       <c r="F141" s="7" t="inlineStr"/>
       <c r="G141" s="7" t="inlineStr"/>
       <c r="H141" s="7" t="inlineStr"/>
@@ -4899,8 +4894,16 @@
       </c>
       <c r="B142" s="7" t="inlineStr"/>
       <c r="C142" s="7" t="inlineStr"/>
-      <c r="D142" s="7" t="inlineStr"/>
-      <c r="E142" s="7" t="inlineStr"/>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (PHY)</t>
+        </is>
+      </c>
       <c r="F142" s="7" t="inlineStr"/>
       <c r="G142" s="7" t="inlineStr"/>
       <c r="H142" s="7" t="inlineStr"/>
@@ -4913,17 +4916,17 @@
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr"/>
-      <c r="C143" s="7" t="inlineStr">
+      <c r="C143" s="7" t="inlineStr"/>
+      <c r="D143" s="7" t="inlineStr">
         <is>
           <t>Class 10 (PHY)</t>
         </is>
       </c>
-      <c r="D143" s="7" t="inlineStr">
+      <c r="E143" s="7" t="inlineStr">
         <is>
           <t>Class 9 (PHY)</t>
         </is>
       </c>
-      <c r="E143" s="7" t="inlineStr"/>
       <c r="F143" s="7" t="inlineStr"/>
       <c r="G143" s="7" t="inlineStr"/>
       <c r="H143" s="7" t="inlineStr"/>
@@ -4937,10 +4940,14 @@
       </c>
       <c r="B144" s="7" t="inlineStr"/>
       <c r="C144" s="7" t="inlineStr"/>
-      <c r="D144" s="7" t="inlineStr"/>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (PHY)</t>
+        </is>
+      </c>
       <c r="E144" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (PHY)</t>
+          <t>Class 10 (PHY)</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
@@ -4961,7 +4968,11 @@
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr"/>
-      <c r="E145" s="7" t="inlineStr"/>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (PHY)</t>
+        </is>
+      </c>
       <c r="F145" s="7" t="inlineStr"/>
       <c r="G145" s="7" t="inlineStr"/>
       <c r="H145" s="7" t="inlineStr"/>
@@ -5037,30 +5048,34 @@
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
+          <t>LKG (ORAL)</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
+        <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
           <t>LKG (EVS)</t>
         </is>
       </c>
-      <c r="C149" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ORAL)</t>
-        </is>
-      </c>
-      <c r="D149" s="7" t="inlineStr">
-        <is>
-          <t>LKG (MATH)</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
           <t>LKG (EVS)</t>
         </is>
       </c>
-      <c r="G149" s="7" t="inlineStr"/>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>LKG (EVS)</t>
+        </is>
+      </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
           <t>LKG (MATH)</t>
@@ -5080,33 +5095,33 @@
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>LKG (EVS)</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
           <t>LKG (ENG)</t>
         </is>
       </c>
-      <c r="C150" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ORAL)</t>
-        </is>
-      </c>
-      <c r="D150" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="E150" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>LKG (ENG)</t>
+          <t>LKG (EVS)</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr"/>
       <c r="H150" s="7" t="inlineStr">
         <is>
-          <t>LKG (MATH)</t>
+          <t>LKG (ORAL)</t>
         </is>
       </c>
       <c r="I150" s="8" t="inlineStr">
@@ -5123,27 +5138,27 @@
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
+          <t>LKG (ORAL)</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="inlineStr">
+        <is>
           <t>LKG (ENG)</t>
         </is>
       </c>
-      <c r="C151" s="7" t="inlineStr">
-        <is>
-          <t>LKG (EVS)</t>
-        </is>
-      </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>LKG (ORAL)</t>
+          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="E151" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
           <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="F151" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
@@ -5170,33 +5185,33 @@
       </c>
       <c r="B152" s="7" t="inlineStr">
         <is>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
           <t>LKG (ENG)</t>
         </is>
       </c>
-      <c r="C152" s="7" t="inlineStr">
-        <is>
-          <t>LKG (EVS)</t>
-        </is>
-      </c>
-      <c r="D152" s="7" t="inlineStr">
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="inlineStr">
         <is>
           <t>LKG (ORAL)</t>
-        </is>
-      </c>
-      <c r="E152" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="F152" s="7" t="inlineStr">
-        <is>
-          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr"/>
       <c r="H152" s="7" t="inlineStr">
         <is>
-          <t>LKG (MATH)</t>
+          <t>LKG (EVS)</t>
         </is>
       </c>
       <c r="I152" s="8" t="inlineStr">
@@ -5218,32 +5233,28 @@
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>LKG (ENG)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>LKG (ENG)</t>
+          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
+          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
+          <t>LKG (ORAL)</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr"/>
+      <c r="H153" s="7" t="inlineStr">
+        <is>
           <t>LKG (MATH)</t>
-        </is>
-      </c>
-      <c r="G153" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ORAL)</t>
-        </is>
-      </c>
-      <c r="H153" s="7" t="inlineStr">
-        <is>
-          <t>LKG (EVS)</t>
         </is>
       </c>
       <c r="I153" s="8" t="inlineStr">
@@ -5265,39 +5276,35 @@
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>LKG (MATH)</t>
+          <t>LKG (ENG)</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>LKG (MATH)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="E154" s="7" t="inlineStr">
         <is>
-          <t>LKG (MATH)</t>
+          <t>LKG (ORAL)</t>
         </is>
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>LKG (ORAL)</t>
+          <t>LKG (ENG)</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="H154" s="7" t="inlineStr">
+        <is>
           <t>LKG (EVS)</t>
         </is>
       </c>
-      <c r="H154" s="7" t="inlineStr">
-        <is>
-          <t>LKG (EVS)</t>
-        </is>
-      </c>
-      <c r="I154" s="8" t="inlineStr">
-        <is>
-          <t>LKG</t>
-        </is>
-      </c>
+      <c r="I154" s="7" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -5376,12 +5383,12 @@
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="G158" s="7" t="inlineStr">
+      <c r="G158" s="7" t="inlineStr"/>
+      <c r="H158" s="7" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
-      <c r="H158" s="7" t="inlineStr"/>
       <c r="I158" s="8" t="inlineStr">
         <is>
           <t>Class 10 (SOC)</t>
@@ -5454,18 +5461,18 @@
       <c r="E161" s="7" t="inlineStr"/>
       <c r="F161" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr"/>
+      <c r="H161" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
+      <c r="I161" s="8" t="inlineStr">
+        <is>
           <t>Class 10 (SOC)</t>
-        </is>
-      </c>
-      <c r="G161" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
-        </is>
-      </c>
-      <c r="H161" s="7" t="inlineStr"/>
-      <c r="I161" s="8" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
         </is>
       </c>
     </row>
@@ -5481,18 +5488,18 @@
       <c r="E162" s="7" t="inlineStr"/>
       <c r="F162" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr"/>
       <c r="I162" s="8" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 9 (SOC)</t>
         </is>
       </c>
     </row>
@@ -5513,15 +5520,15 @@
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="H163" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="H163" s="7" t="inlineStr"/>
-      <c r="I163" s="8" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
+      <c r="I163" s="7" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -5593,33 +5600,33 @@
       </c>
       <c r="B167" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (G.K)</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (HIN)</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (MATH)</t>
         </is>
       </c>
-      <c r="C167" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (MATH)</t>
-        </is>
-      </c>
-      <c r="D167" s="7" t="inlineStr">
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (EVS)</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (TEL)</t>
         </is>
       </c>
-      <c r="E167" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (HIN)</t>
-        </is>
-      </c>
-      <c r="F167" s="7" t="inlineStr"/>
-      <c r="G167" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (EVS)</t>
-        </is>
-      </c>
+      <c r="G167" s="7" t="inlineStr"/>
       <c r="H167" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (MATH)</t>
+          <t>Class 1(B) (ENG)</t>
         </is>
       </c>
       <c r="I167" s="8" t="inlineStr">
@@ -5636,33 +5643,33 @@
       </c>
       <c r="B168" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (TEL)</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (ENG)</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (ENG)</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (EVS)</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr"/>
+      <c r="G168" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (HIN)</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (G.K)</t>
-        </is>
-      </c>
-      <c r="C168" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (MATH)</t>
-        </is>
-      </c>
-      <c r="D168" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (TEL)</t>
-        </is>
-      </c>
-      <c r="E168" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (ENG)</t>
-        </is>
-      </c>
-      <c r="F168" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (MATH)</t>
-        </is>
-      </c>
-      <c r="G168" s="7" t="inlineStr"/>
-      <c r="H168" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (EVS)</t>
         </is>
       </c>
       <c r="I168" s="8" t="inlineStr">
@@ -5684,25 +5691,25 @@
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (TEL)</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (MATH)</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr"/>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (HIN)</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (ENG)</t>
         </is>
       </c>
-      <c r="D169" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (HIN)</t>
-        </is>
-      </c>
-      <c r="E169" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (G.K)</t>
-        </is>
-      </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (TEL)</t>
-        </is>
-      </c>
-      <c r="G169" s="7" t="inlineStr"/>
       <c r="H169" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (ENG)</t>
@@ -5722,28 +5729,28 @@
       </c>
       <c r="B170" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (EVS)</t>
+        </is>
+      </c>
+      <c r="C170" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (TEL)</t>
         </is>
       </c>
-      <c r="C170" s="7" t="inlineStr">
+      <c r="D170" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (ENG)</t>
         </is>
       </c>
-      <c r="D170" s="7" t="inlineStr"/>
-      <c r="E170" s="7" t="inlineStr">
+      <c r="E170" s="7" t="inlineStr"/>
+      <c r="F170" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (HIN)</t>
         </is>
       </c>
-      <c r="F170" s="7" t="inlineStr">
+      <c r="G170" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (ENG)</t>
-        </is>
-      </c>
-      <c r="G170" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (EVS)</t>
         </is>
       </c>
       <c r="H170" s="7" t="inlineStr"/>
@@ -5761,33 +5768,33 @@
       </c>
       <c r="B171" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (MATH)</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (EVS)</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (MATH)</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (HIN)</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (TEL)</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr"/>
+      <c r="H171" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (ENG)</t>
-        </is>
-      </c>
-      <c r="C171" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (EVS)</t>
-        </is>
-      </c>
-      <c r="D171" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (MATH)</t>
-        </is>
-      </c>
-      <c r="E171" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (TEL)</t>
-        </is>
-      </c>
-      <c r="F171" s="7" t="inlineStr"/>
-      <c r="G171" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (HIN)</t>
-        </is>
-      </c>
-      <c r="H171" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (MATH)</t>
         </is>
       </c>
       <c r="I171" s="8" t="inlineStr">
@@ -5809,22 +5816,22 @@
       </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (ENG)</t>
+          <t>Class 1(B) (MATH)</t>
         </is>
       </c>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (HIN)</t>
+          <t>Class 1(B) (MATH)</t>
         </is>
       </c>
       <c r="E172" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (MATH)</t>
+        </is>
+      </c>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (EVS)</t>
-        </is>
-      </c>
-      <c r="F172" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (ENG)</t>
         </is>
       </c>
       <c r="G172" s="7" t="inlineStr"/>
@@ -5833,11 +5840,7 @@
           <t>Class 1(B) (TEL)</t>
         </is>
       </c>
-      <c r="I172" s="8" t="inlineStr">
-        <is>
-          <t>Class 1(B)</t>
-        </is>
-      </c>
+      <c r="I172" s="7" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
@@ -5907,15 +5910,15 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B176" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (COMP)</t>
-        </is>
-      </c>
-      <c r="C176" s="7" t="inlineStr"/>
+      <c r="B176" s="7" t="inlineStr"/>
+      <c r="C176" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (COMP)</t>
+        </is>
+      </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (COMP)</t>
+          <t>Class 2 (COMP)</t>
         </is>
       </c>
       <c r="E176" s="7" t="inlineStr">
@@ -5923,11 +5926,7 @@
           <t>Class 1(A) (COMP)</t>
         </is>
       </c>
-      <c r="F176" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (COMP)</t>
-        </is>
-      </c>
+      <c r="F176" s="7" t="inlineStr"/>
       <c r="G176" s="7" t="inlineStr"/>
       <c r="H176" s="7" t="inlineStr"/>
       <c r="I176" s="7" t="inlineStr"/>
@@ -5938,10 +5937,14 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B177" s="7" t="inlineStr"/>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (COMP)</t>
+        </is>
+      </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (COMP)</t>
+          <t>Class 3 (COMP)</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
@@ -5949,13 +5952,17 @@
           <t>Class 2 (COMP)</t>
         </is>
       </c>
-      <c r="E177" s="7" t="inlineStr">
+      <c r="E177" s="7" t="inlineStr"/>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (COMP)</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (COMP)</t>
         </is>
       </c>
-      <c r="F177" s="7" t="inlineStr"/>
-      <c r="G177" s="7" t="inlineStr"/>
       <c r="H177" s="7" t="inlineStr"/>
       <c r="I177" s="7" t="inlineStr"/>
     </row>
@@ -5965,28 +5972,28 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B178" s="7" t="inlineStr"/>
+      <c r="B178" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (COMP)</t>
+        </is>
+      </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (COMP)</t>
-        </is>
-      </c>
-      <c r="D178" s="7" t="inlineStr">
-        <is>
           <t>Class 3 (COMP)</t>
         </is>
       </c>
+      <c r="D178" s="7" t="inlineStr"/>
       <c r="E178" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (COMP)</t>
-        </is>
-      </c>
-      <c r="F178" s="7" t="inlineStr"/>
-      <c r="G178" s="7" t="inlineStr">
+          <t>Class 1(B) (COMP)</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (COMP)</t>
         </is>
       </c>
+      <c r="G178" s="7" t="inlineStr"/>
       <c r="H178" s="7" t="inlineStr"/>
       <c r="I178" s="7" t="inlineStr"/>
     </row>
@@ -5996,20 +6003,20 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B179" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (COMP)</t>
-        </is>
-      </c>
-      <c r="C179" s="7" t="inlineStr"/>
+      <c r="B179" s="7" t="inlineStr"/>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (COMP)</t>
+        </is>
+      </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (COMP)</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (COMP)</t>
-        </is>
-      </c>
-      <c r="E179" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (COMP)</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
@@ -6023,27 +6030,23 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B180" s="7" t="inlineStr">
+      <c r="B180" s="7" t="inlineStr"/>
+      <c r="C180" s="7" t="inlineStr">
         <is>
           <t>Class 5 (COMP)</t>
         </is>
       </c>
-      <c r="C180" s="7" t="inlineStr"/>
       <c r="D180" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (COMP)</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (COMP)</t>
         </is>
       </c>
-      <c r="E180" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (COMP)</t>
-        </is>
-      </c>
-      <c r="F180" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (COMP)</t>
-        </is>
-      </c>
+      <c r="F180" s="7" t="inlineStr"/>
       <c r="G180" s="7" t="inlineStr"/>
       <c r="H180" s="7" t="inlineStr"/>
       <c r="I180" s="7" t="inlineStr"/>
@@ -6057,12 +6060,12 @@
       <c r="B181" s="7" t="inlineStr"/>
       <c r="C181" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (COMP)</t>
+          <t>Class 7 (COMP)</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (COMP)</t>
+          <t>Class 4 (COMP)</t>
         </is>
       </c>
       <c r="E181" s="7" t="inlineStr">
@@ -6150,12 +6153,12 @@
       <c r="F185" s="7" t="inlineStr"/>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (P.E.T)</t>
+          <t>Class 10 (P.E.T)</t>
         </is>
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (P.E.T)</t>
+          <t>Class 1(A) (P.E.T)</t>
         </is>
       </c>
       <c r="I185" s="7" t="inlineStr"/>
@@ -6173,12 +6176,12 @@
       <c r="F186" s="7" t="inlineStr"/>
       <c r="G186" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (P.E.T)</t>
+          <t>Class 9 (P.E.T)</t>
         </is>
       </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (P.E.T)</t>
+          <t>Class 6 (P.E.T)</t>
         </is>
       </c>
       <c r="I186" s="7" t="inlineStr"/>
@@ -6196,7 +6199,7 @@
       <c r="F187" s="7" t="inlineStr"/>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (P.E.T)</t>
+          <t>Class 2 (P.E.T)</t>
         </is>
       </c>
       <c r="H187" s="7" t="inlineStr">
@@ -6219,7 +6222,7 @@
       <c r="F188" s="7" t="inlineStr"/>
       <c r="G188" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (P.E.T)</t>
+          <t>Class 5 (P.E.T)</t>
         </is>
       </c>
       <c r="H188" s="7" t="inlineStr"/>
@@ -6238,12 +6241,12 @@
       <c r="F189" s="7" t="inlineStr"/>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (P.E.T)</t>
+          <t>Class 2 (P.E.T)</t>
         </is>
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (P.E.T)</t>
+          <t>Class 4 (P.E.T)</t>
         </is>
       </c>
       <c r="I189" s="7" t="inlineStr"/>
@@ -6261,7 +6264,7 @@
       <c r="F190" s="7" t="inlineStr"/>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (P.E.T)</t>
+          <t>Class 10 (P.E.T)</t>
         </is>
       </c>
       <c r="H190" s="7" t="inlineStr">
@@ -6578,61 +6581,61 @@
       <c r="C2" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="K2" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(G.K)</t>
-        </is>
-      </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(BIO)</t>
+          <t>R.KAMALA
+(SOC)</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -6643,20 +6646,20 @@
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>K.ESWAR
+(PHY)</t>
         </is>
       </c>
       <c r="O2" s="7" t="inlineStr">
-        <is>
-          <t>SAIRAM
-(PHY)</t>
-        </is>
-      </c>
-      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
+        </is>
+      </c>
+      <c r="P2" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6671,7 @@
       <c r="C3" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -6680,7 +6683,7 @@
       <c r="E3" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -6692,7 +6695,7 @@
       <c r="G3" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(MATH)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -6703,28 +6706,28 @@
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
+          <t>D.SUMANI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
@@ -6733,19 +6736,20 @@
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="O3" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="P3" s="7" t="inlineStr">
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (CHEM)</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -6763,72 +6767,73 @@
       <c r="D4" s="7" t="inlineStr">
         <is>
           <t>BIJILI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (EVS)</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (TEL)</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(HIN)</t>
-        </is>
-      </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(TEL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>R.KAMALA
-(SOC)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(EVS)</t>
-        </is>
-      </c>
-      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
       <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="O4" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
@@ -6845,83 +6850,86 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>SHEKINA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
       <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(EVS)</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="N5" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="O5" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="P5" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -6939,55 +6947,55 @@
       <c r="D6" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(EVS)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(G.K)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>SURYA DEVI
+(TEL)</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(EVS)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>D.SUMANI
-(G.K)</t>
+          <t>R.KAMALA
+(SOC)</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -6998,8 +7006,8 @@
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(PHY)</t>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
       <c r="O6" s="7" t="inlineStr">
@@ -7022,34 +7030,34 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ORAL)</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(EVS)</t>
-        </is>
-      </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
@@ -7058,8 +7066,8 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+          <t>P.E.T Instructor
+(P.E.T)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -7070,38 +7078,38 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
       <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>D.GOWTHAM
 (MATH)</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
         </is>
       </c>
     </row>
@@ -7119,13 +7127,13 @@
       <c r="D8" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(EVS)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -7137,7 +7145,7 @@
       <c r="G8" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -7149,49 +7157,49 @@
       <c r="I8" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(CHEM)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>D.GOWTHAM
+(MATH)</t>
         </is>
       </c>
     </row>
@@ -7299,19 +7307,19 @@
       <c r="C10" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(MATH)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -7323,7 +7331,7 @@
       <c r="G10" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(G.K)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -7346,26 +7354,26 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
+          <t>K.ESWAR
+(EVS)</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(PHY)</t>
+          <t>VINAY
+(COMP)</t>
         </is>
       </c>
       <c r="O10" s="7" t="inlineStr">
@@ -7388,8 +7396,8 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
-(ORAL)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -7401,72 +7409,73 @@
       <c r="E11" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (ENG)</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>SHEKINA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (PHY)</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="O11" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -7478,31 +7487,31 @@
       <c r="C12" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(TEL)</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -7514,21 +7523,21 @@
       <c r="I12" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
@@ -7537,26 +7546,26 @@
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>R.KAMALA
-(SOC)</t>
+          <t>K.ESWAR
+(PHY)</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -7567,85 +7576,86 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ORAL)</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ORAL)</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>SHEKINA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (CHEM)</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N13" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>SAIRAM
-(PHY)</t>
         </is>
       </c>
     </row>
@@ -7657,19 +7667,19 @@
       <c r="C14" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(MATH)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -7680,8 +7690,8 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>SURYA DEVI
-(MATH)</t>
+          <t>VINAY
+(COMP)</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -7692,8 +7702,8 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+          <t>R.KAMALA
+(SOC)</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
@@ -7705,7 +7715,7 @@
       <c r="K14" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(EVS)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -7716,8 +7726,8 @@
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>CHANDINI
-(MATH)</t>
+          <t>SAI KEERTHI
+(HIN)</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
@@ -7753,7 +7763,7 @@
       <c r="D15" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(EVS)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -7764,62 +7774,62 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
           <t>CHANDRAKALA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(G.K)</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
@@ -7837,19 +7847,19 @@
       <c r="C16" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(TEL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -7861,7 +7871,7 @@
       <c r="G16" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(EVS)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -7872,50 +7882,50 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
+(BIO)</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
       <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>D.GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
         </is>
       </c>
     </row>
@@ -8023,25 +8033,25 @@
       <c r="C18" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (ENG)</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ORAL)</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(HIN)</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
@@ -8070,8 +8080,8 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>SAI KEERTHI
-(HIN)</t>
+          <t>VINAY
+(COMP)</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -8098,9 +8108,10 @@
 (TEL)</t>
         </is>
       </c>
-      <c r="P18" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -8112,19 +8123,19 @@
       <c r="C19" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
 (EVS)</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ENG)</t>
-        </is>
-      </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -8136,7 +8147,7 @@
       <c r="G19" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(ENG)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -8147,44 +8158,44 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>R.KAMALA
-(SOC)</t>
+          <t>K.ESWAR
+(CHEM)</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
@@ -8202,31 +8213,31 @@
       <c r="C20" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
 (ORAL)</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (TEL)</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(EVS)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(HIN)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -8237,8 +8248,8 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
@@ -8249,38 +8260,38 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
       <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>SAIRAM
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -8291,8 +8302,8 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
-(ENG)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -8310,25 +8321,25 @@
       <c r="F21" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(TEL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>SHEKINA
+(HIN)</t>
+        </is>
+      </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+          <t>SAI KEERTHI
+(HIN)</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
@@ -8345,30 +8356,32 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(G.K)</t>
+          <t>M.LALITHA
+(TEL)</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N21" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="O21" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
+          <t>S.GAYATHRI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -8379,74 +8392,74 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(PHY)</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
 (ENG)</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>SHEKINA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(EVS)</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
         </is>
       </c>
       <c r="O22" s="7" t="inlineStr">
@@ -8475,32 +8488,32 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>BIJILI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(ENG)</t>
+        </is>
+      </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>CHANDRAKALA
-(MATH)</t>
+          <t>P.E.T Instructor
+(P.E.T)</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -8511,22 +8524,22 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(EVS)</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
@@ -8535,8 +8548,8 @@
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>D.SUMANI
-(ENG)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="O23" s="7" t="inlineStr">
@@ -8566,13 +8579,13 @@
       <c r="D24" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(TEL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -8619,14 +8632,14 @@
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
           <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="O24" s="7" t="inlineStr">
@@ -8746,13 +8759,13 @@
       <c r="C26" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(MATH)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -8764,39 +8777,39 @@
       <c r="F26" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (EVS)</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(TEL)</t>
-        </is>
-      </c>
       <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
@@ -8811,14 +8824,14 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
         </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
@@ -8836,37 +8849,37 @@
       <c r="C27" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (EVS)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (HIN)</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
 (ENG)</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(G.K)</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -8883,14 +8896,14 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>N.NAVYA
-(ENG)</t>
+          <t>CHANDINI
+(MATH)</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(PHY)</t>
+          <t>S.GAYATHRI
+(BIO)</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -8901,20 +8914,20 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>CHANDINI
-(MATH)</t>
+          <t>VINAY
+(COMP)</t>
         </is>
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>D.SUMANI
-(ENG)</t>
+          <t>K.ESWAR
+(CHEM)</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>SAIRAM
-(PHY)</t>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -8926,19 +8939,19 @@
       <c r="C28" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
           <t>BIJILI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (MATH)</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ORAL)</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -8949,61 +8962,62 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
+          <t>SURYA DEVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(EVS)</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
+(PHY)</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
         </is>
       </c>
-      <c r="N28" s="7" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
         </is>
       </c>
-      <c r="O28" s="7" t="inlineStr">
+      <c r="P28" s="7" t="inlineStr">
         <is>
           <t>SAIRAM
 (PHY)</t>
-        </is>
-      </c>
-      <c r="P28" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9021,25 +9035,25 @@
       <c r="D29" s="7" t="inlineStr">
         <is>
           <t>BIJILI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (TEL)</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(MATH)</t>
-        </is>
-      </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(HIN)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>SURYA DEVI
-(HIN)</t>
+          <t>VINAY
+(COMP)</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -9050,16 +9064,16 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
           <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(G.K)</t>
-        </is>
-      </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
@@ -9068,30 +9082,32 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>SAI KEERTHI
-(HIN)</t>
+          <t>N.NAVYA
+(ENG)</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="N29" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
         </is>
       </c>
       <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
+        </is>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="P29" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9103,57 +9119,57 @@
       <c r="C30" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
           <t>BIJILI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (ENG)</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(TEL)</t>
-        </is>
-      </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(ENG)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
       <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(EVS)</t>
+        </is>
+      </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
@@ -9168,20 +9184,20 @@
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
           <t>D.SUMANI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="O30" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="P30" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -9204,52 +9220,52 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
+          <t>MAHA LAKSHMI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(G.K)</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
@@ -9258,20 +9274,20 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="O31" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="P31" s="7" t="inlineStr">
-        <is>
           <t>M.LALITHA
 (TEL)</t>
+        </is>
+      </c>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>D.GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -9283,19 +9299,19 @@
       <c r="C32" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ORAL)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -9354,8 +9370,8 @@
       </c>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>D.GOWTHAM
-(MATH)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
       <c r="P32" s="7" t="inlineStr">
@@ -9440,22 +9456,22 @@
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>D.GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="P33" s="8" t="inlineStr">
+        <is>
           <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="O33" s="8" t="inlineStr">
-        <is>
-          <t>D.GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
-      <c r="P33" s="8" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
     </row>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
@@ -9475,13 +9491,13 @@
       <c r="D34" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(TEL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(HIN)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -9493,7 +9509,7 @@
       <c r="G34" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -9504,22 +9520,22 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
+          <t>S.GAYATHRI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
@@ -9528,26 +9544,26 @@
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(BIO)</t>
+          <t>CHANDINI
+(MATH)</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(G.K)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="O34" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="P34" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -9558,26 +9574,26 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (ENG)</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(EVS)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -9588,54 +9604,56 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
           <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (CHEM)</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="N35" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
       <c r="O35" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="P35" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9647,7 +9665,7 @@
       <c r="C36" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -9659,7 +9677,7 @@
       <c r="E36" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ORAL)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -9688,44 +9706,44 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(EVS)</t>
-        </is>
-      </c>
-      <c r="L36" s="7" t="inlineStr">
-        <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="M36" s="7" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>M.LALITHA
-(TEL)</t>
+          <t>K.ESWAR
+(G.K)</t>
         </is>
       </c>
       <c r="O36" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
+        </is>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="P36" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -9736,85 +9754,86 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>SHEKINA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(G.K)</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="N37" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
         </is>
       </c>
-      <c r="N37" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="O37" s="7" t="inlineStr">
+      <c r="P37" s="7" t="inlineStr">
         <is>
           <t>SAIRAM
 (PHY)</t>
-        </is>
-      </c>
-      <c r="P37" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9826,19 +9845,19 @@
       <c r="C38" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (MATH)</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(TEL)</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -9849,8 +9868,8 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>SURYA DEVI
+(TEL)</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
@@ -9861,8 +9880,8 @@
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(MATH)</t>
+          <t>SAI KEERTHI
+(HIN)</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr">
@@ -9879,32 +9898,32 @@
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(PHY)</t>
+          <t>CHANDINI
+(MATH)</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>SAI KEERTHI
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="O38" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
 (HIN)</t>
         </is>
       </c>
-      <c r="N38" s="7" t="inlineStr">
+      <c r="P38" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="O38" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="P38" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -9915,52 +9934,52 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
-(ORAL)</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(ENG)</t>
+        </is>
+      </c>
       <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
@@ -9969,26 +9988,26 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
+          <t>M.LALITHA
+(TEL)</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>R.KAMALA
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="N39" s="7" t="inlineStr">
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (CHEM)</t>
-        </is>
-      </c>
-      <c r="O39" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
@@ -10006,19 +10025,19 @@
       <c r="C40" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
           <t>BIJILI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (ORAL)</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(EVS)</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -10030,7 +10049,7 @@
       <c r="G40" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
@@ -10041,50 +10060,50 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+          <t>S.GAYATHRI
+(MATH)</t>
         </is>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
 (EVS)</t>
         </is>
       </c>
-      <c r="K40" s="7" t="inlineStr">
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="M40" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
       <c r="O40" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="P40" s="7" t="inlineStr">
         <is>
           <t>D.GOWTHAM
 (MATH)</t>
+        </is>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -10169,16 +10188,16 @@
       </c>
       <c r="O41" s="8" t="inlineStr">
         <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="P41" s="8" t="inlineStr">
+        <is>
           <t>D.GOWTHAM
 (MATH)</t>
         </is>
       </c>
-      <c r="P41" s="8" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
@@ -10198,13 +10217,13 @@
       <c r="D42" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -10233,22 +10252,22 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="K42" s="7" t="inlineStr">
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="L42" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
@@ -10257,8 +10276,8 @@
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>K.ESWAR
+(PHY)</t>
         </is>
       </c>
       <c r="O42" s="7" t="inlineStr">
@@ -10269,8 +10288,8 @@
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(CHEM)</t>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -10282,31 +10301,31 @@
       <c r="C43" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (MATH)</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(ENG)</t>
-        </is>
-      </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
@@ -10323,32 +10342,32 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L43" s="7" t="inlineStr">
-        <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
       <c r="M43" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N43" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
         </is>
       </c>
       <c r="O43" s="7" t="inlineStr">
@@ -10371,85 +10390,86 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
           <t>SHEKINA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
 (MATH)</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ORAL)</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
+      <c r="M44" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="O44" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
 (ENG)</t>
         </is>
       </c>
-      <c r="L44" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="M44" s="7" t="inlineStr">
+      <c r="P44" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (CHEM)</t>
-        </is>
-      </c>
-      <c r="N44" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="O44" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="P44" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -10461,31 +10481,31 @@
       <c r="C45" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (MATH)</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(EVS)</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -10502,37 +10522,38 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(EVS)</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="K45" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L45" s="7" t="inlineStr">
+      <c r="M45" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(PHY)</t>
-        </is>
-      </c>
-      <c r="N45" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="O45" s="7" t="inlineStr">
+      <c r="N45" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
+        </is>
+      </c>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
@@ -10550,7 +10571,7 @@
       <c r="C46" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -10562,55 +10583,55 @@
       <c r="E46" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
       <c r="K46" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(EVS)</t>
-        </is>
-      </c>
-      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="M46" s="7" t="inlineStr">
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
@@ -10640,7 +10661,7 @@
       <c r="C47" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -10651,74 +10672,74 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
+          <t>MAHA LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr">
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(G.K)</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>D.GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="L47" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="N47" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="O47" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="P47" s="7" t="inlineStr">
-        <is>
-          <t>D.GOWTHAM
-(MATH)</t>
         </is>
       </c>
     </row>
@@ -10736,13 +10757,13 @@
       <c r="D48" s="7" t="inlineStr">
         <is>
           <t>BIJILI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (MATH)</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(EVS)</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -10765,44 +10786,44 @@
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(EVS)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="K48" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
       <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M48" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
-      <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
       <c r="N48" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="O48" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (CHEM)</t>
+        </is>
+      </c>
+      <c r="O48" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
@@ -10819,90 +10840,20 @@
           <t>Study Hour</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>SHEKINA
-(CLASS)</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>BIJILI
-(CLASS)</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(CLASS)</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(CLASS)</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(CLASS)</t>
-        </is>
-      </c>
-      <c r="H49" s="8" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(CLASS)</t>
-        </is>
-      </c>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(CLASS)</t>
-        </is>
-      </c>
-      <c r="J49" s="8" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(CLASS)</t>
-        </is>
-      </c>
-      <c r="K49" s="8" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CLASS)</t>
-        </is>
-      </c>
-      <c r="L49" s="8" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(CLASS)</t>
-        </is>
-      </c>
-      <c r="M49" s="8" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(CLASS)</t>
-        </is>
-      </c>
-      <c r="N49" s="8" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="O49" s="8" t="inlineStr">
-        <is>
-          <t>D.GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
-      <c r="P49" s="8" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
+      <c r="C49" s="12" t="inlineStr"/>
+      <c r="D49" s="12" t="inlineStr"/>
+      <c r="E49" s="12" t="inlineStr"/>
+      <c r="F49" s="12" t="inlineStr"/>
+      <c r="G49" s="12" t="inlineStr"/>
+      <c r="H49" s="12" t="inlineStr"/>
+      <c r="I49" s="12" t="inlineStr"/>
+      <c r="J49" s="12" t="inlineStr"/>
+      <c r="K49" s="12" t="inlineStr"/>
+      <c r="L49" s="12" t="inlineStr"/>
+      <c r="M49" s="12" t="inlineStr"/>
+      <c r="N49" s="12" t="inlineStr"/>
+      <c r="O49" s="12" t="inlineStr"/>
+      <c r="P49" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="6">
